--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/sep-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/sep-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/sep-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -904,7 +904,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>550716-12-CM26</t>
+          <t>558338-4-SE26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6943.58</v>
+        <v>306084.36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1186801-10-CM26</t>
+          <t>550716-12-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4681.22</v>
+        <v>6943.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2702-464-CM26</t>
+          <t>1186801-10-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10413.64</v>
+        <v>4681.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>307-95-CM26</t>
+          <t>2702-464-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>667.67</v>
+        <v>10413.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>307-96-CM26</t>
+          <t>307-95-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>307-97-CM26</t>
+          <t>307-96-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>307-98-CM26</t>
+          <t>307-97-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2701-675-CM26</t>
+          <t>307-98-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2701-676-CM26</t>
+          <t>2701-675-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2701-677-CM26</t>
+          <t>2701-676-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1554,7 +1554,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1477-295-CM26</t>
+          <t>2701-677-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1613,71 +1613,136 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35397.27</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>1477-295-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>35397.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>1495206-6-CM26</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>61.981.340-5</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>20926.2</v>
       </c>
     </row>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/sep-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/sep-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
